--- a/02.FOMD/02.metadata_structure/REMOVE_FOMD_outcomes.xlsx
+++ b/02.FOMD/02.metadata_structure/REMOVE_FOMD_outcomes.xlsx
@@ -11863,8 +11863,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="25f56b0caabe45c534a8a23e8652b075">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2a31fe97de8c49c1f148ae9862b2aa2d" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -11882,6 +11882,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -11934,6 +11935,11 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -12071,7 +12077,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E17B954-56FD-40D2-87F6-8401A9B11CDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CF66057-02F1-45DB-AEA9-5AC935D2087E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
